--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\12 MATHS NOTES AND  STUDY MAT 2025-26\Class Tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirti\OneDrive\Desktop\mydiarykv\class test\class test 12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2865A6-6B9F-42C5-846E-E9763BD96C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478B2D8C-A210-44AF-A3F0-1E0C4F5C7080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>mixed</t>
+  </si>
+  <si>
+    <t>ch7</t>
+  </si>
+  <si>
+    <t>souvik</t>
   </si>
 </sst>
 </file>
@@ -182,7 +188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -242,11 +248,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -273,51 +299,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -634,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.54296875" customWidth="1"/>
@@ -694,6 +687,9 @@
       <c r="H3" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="J3" s="16" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
@@ -717,6 +713,9 @@
       </c>
       <c r="H4" s="6">
         <v>46182</v>
+      </c>
+      <c r="J4" s="17">
+        <v>46231</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -742,6 +741,9 @@
       <c r="H5" s="5">
         <v>20</v>
       </c>
+      <c r="J5" s="18">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -768,6 +770,9 @@
       <c r="H6" s="7">
         <v>5</v>
       </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -794,6 +799,9 @@
       <c r="H7" s="7">
         <v>4</v>
       </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -820,6 +828,9 @@
       <c r="H8" s="7">
         <v>0</v>
       </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -846,6 +857,9 @@
       <c r="H9" s="7">
         <v>5</v>
       </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -872,6 +886,9 @@
       <c r="H10" s="7">
         <v>3</v>
       </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -898,6 +915,9 @@
       <c r="H11" s="7">
         <v>20</v>
       </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -924,6 +944,9 @@
       <c r="H12" s="7">
         <v>14</v>
       </c>
+      <c r="J12">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -950,6 +973,9 @@
       <c r="H13" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
@@ -976,6 +1002,9 @@
       <c r="H14" s="7">
         <v>2</v>
       </c>
+      <c r="J14">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1002,6 +1031,9 @@
       <c r="H15" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="J15">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -1028,8 +1060,11 @@
       <c r="H16" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -1054,8 +1089,11 @@
       <c r="H17" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>13</v>
       </c>
@@ -1080,8 +1118,11 @@
       <c r="H18" s="7">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>14</v>
       </c>
@@ -1106,8 +1147,11 @@
       <c r="H19" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>15</v>
       </c>
@@ -1132,8 +1176,11 @@
       <c r="H20" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>16</v>
       </c>
@@ -1158,8 +1205,11 @@
       <c r="H21" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>17</v>
       </c>
@@ -1184,8 +1234,11 @@
       <c r="H22" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>18</v>
       </c>
@@ -1210,8 +1263,11 @@
       <c r="H23" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>19</v>
       </c>
@@ -1236,8 +1292,11 @@
       <c r="H24" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>20</v>
       </c>
@@ -1262,8 +1321,11 @@
       <c r="H25" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>21</v>
       </c>
@@ -1288,8 +1350,11 @@
       <c r="H26" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J26">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>22</v>
       </c>
@@ -1314,8 +1379,11 @@
       <c r="H27" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -1339,6 +1407,20 @@
       </c>
       <c r="H28" s="11">
         <v>8</v>
+      </c>
+      <c r="J28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>24</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1348,24 +1430,24 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B27:F28">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="ab">
+  <conditionalFormatting sqref="B27:F28 B29">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="ab">
       <formula>NOT(ISERROR(SEARCH("ab",B27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:F27">
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="ab">
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="ab">
       <formula>NOT(ISERROR(SEARCH("ab",C6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13 H15 G14:G15">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="ab">
-      <formula>NOT(ISERROR(SEARCH("ab",G13)))</formula>
+  <conditionalFormatting sqref="G25 G27">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="ab">
+      <formula>NOT(ISERROR(SEARCH("ab",G25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27 G25">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="ab">
-      <formula>NOT(ISERROR(SEARCH("ab",G25)))</formula>
+  <conditionalFormatting sqref="H13 G14:G15 H15">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="ab">
+      <formula>NOT(ISERROR(SEARCH("ab",G13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -1,44 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirti\OneDrive\Desktop\mydiarykv\class test\class test 12\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$F$5</definedName>
   </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+  <si>
+    <t>PM SHRI KV RANIKHET</t>
+  </si>
+  <si>
+    <t>CLASS 12 MATHEMATICS 2026-27 (CLASS TEST RECORD)</t>
+  </si>
+  <si>
+    <t>CHAPTERS</t>
+  </si>
+  <si>
+    <t>ch1</t>
+  </si>
+  <si>
+    <t>ch2</t>
+  </si>
+  <si>
+    <t>ch3</t>
+  </si>
+  <si>
+    <t>ch4</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>ch5</t>
+  </si>
+  <si>
+    <t>ch6</t>
+  </si>
+  <si>
+    <t>DATES</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ABHIMANYU SINGH</t>
+  </si>
+  <si>
+    <t>ANUJ GOSWAMI</t>
+  </si>
+  <si>
+    <t>AYUSH NEGI</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>BHUMI SATI</t>
+  </si>
+  <si>
+    <t>HARDIK PHULARA</t>
+  </si>
+  <si>
+    <t>HARSHIT ARYA</t>
+  </si>
+  <si>
+    <t>HARSHITA NEGI</t>
+  </si>
+  <si>
+    <t>HITESH UPADHYAY</t>
+  </si>
+  <si>
+    <t>KAMAL JOSHI</t>
+  </si>
+  <si>
+    <t>KANIKA BISHT</t>
+  </si>
+  <si>
+    <t>KARAN</t>
+  </si>
+  <si>
+    <t>NITIN BISHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARTH </t>
+  </si>
+  <si>
+    <t>PRIYANKA</t>
+  </si>
+  <si>
+    <t>RAJ</t>
+  </si>
+  <si>
+    <t>RITIKA</t>
+  </si>
+  <si>
+    <t>SADHNA</t>
+  </si>
+  <si>
+    <t>SAKSHAM NEGI</t>
+  </si>
+  <si>
+    <t>SIYA SUYAL</t>
+  </si>
+  <si>
+    <t>SPARSH BHATT</t>
+  </si>
+  <si>
+    <t>TANMAY ADHIKARI</t>
+  </si>
+  <si>
+    <t>PALAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NISHANT </t>
+  </si>
+  <si>
+    <t>souvik</t>
+  </si>
+  <si>
+    <t>ch7(indefinite Integral)</t>
+  </si>
+  <si>
+    <t>ch7(definite Intrgral)</t>
+  </si>
+  <si>
+    <t>31/07/2026)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,14 +178,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -399,80 +519,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PM SHRI KV RANIKHET</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>CLASS 12 MATHEMATICS 2026-27 (CLASS TEST RECORD)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>CHAPTERS</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ch1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>ch2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>ch3</v>
-      </c>
-      <c r="F3" t="str">
-        <v>ch4</v>
-      </c>
-      <c r="G3" t="str">
-        <v>mixed</v>
-      </c>
-      <c r="H3" t="str">
-        <v>ch5</v>
-      </c>
-      <c r="I3" t="str">
-        <v>ch6</v>
-      </c>
-      <c r="J3" t="str">
-        <v>ch7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>DATES</v>
-      </c>
-      <c r="C4">
+    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
         <v>46125</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>46132</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>46114</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>46120</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>46175</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>46182</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>46195</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>46231</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="str">
-        <v>NAME</v>
+      <c r="K4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -498,13 +631,16 @@
       <c r="J5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" t="str">
-        <v>ABHIMANYU SINGH</v>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -531,12 +667,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" t="str">
-        <v>ANUJ GOSWAMI</v>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -562,13 +698,16 @@
       <c r="J7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="K7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
-      <c r="B8" t="str">
-        <v>AYUSH NEGI</v>
+      <c r="B8" t="s">
+        <v>14</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -576,8 +715,8 @@
       <c r="D8">
         <v>11</v>
       </c>
-      <c r="E8" t="str">
-        <v>ab</v>
+      <c r="E8" t="s">
+        <v>15</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -594,19 +733,22 @@
       <c r="J8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="K8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="B9" t="str">
-        <v>BHUMI SATI</v>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>15</v>
       </c>
-      <c r="D9" t="str">
-        <v>ab</v>
+      <c r="D9" t="s">
+        <v>15</v>
       </c>
       <c r="E9">
         <v>15</v>
@@ -626,13 +768,16 @@
       <c r="J9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="K9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5</v>
       </c>
-      <c r="B10" t="str">
-        <v>HARDIK PHULARA</v>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -658,13 +803,16 @@
       <c r="J10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="K10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" t="str">
-        <v>HARSHIT ARYA</v>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -690,13 +838,16 @@
       <c r="J11">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="K11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>7</v>
       </c>
-      <c r="B12" t="str">
-        <v>HARSHITA NEGI</v>
+      <c r="B12" t="s">
+        <v>19</v>
       </c>
       <c r="C12">
         <v>17</v>
@@ -722,13 +873,16 @@
       <c r="J12">
         <v>19</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="K12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>8</v>
       </c>
-      <c r="B13" t="str">
-        <v>HITESH UPADHYAY</v>
+      <c r="B13" t="s">
+        <v>20</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -745,8 +899,8 @@
       <c r="G13">
         <v>2</v>
       </c>
-      <c r="H13" t="str">
-        <v>ab</v>
+      <c r="H13" t="s">
+        <v>15</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -754,13 +908,16 @@
       <c r="J13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="K13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>9</v>
       </c>
-      <c r="B14" t="str">
-        <v>KAMAL JOSHI</v>
+      <c r="B14" t="s">
+        <v>21</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -768,14 +925,14 @@
       <c r="D14">
         <v>8</v>
       </c>
-      <c r="E14" t="str">
-        <v>ab</v>
+      <c r="E14" t="s">
+        <v>15</v>
       </c>
       <c r="F14">
         <v>5.5</v>
       </c>
-      <c r="G14" t="str">
-        <v>ab</v>
+      <c r="G14" t="s">
+        <v>15</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -786,13 +943,16 @@
       <c r="J14">
         <v>14</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="K14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10</v>
       </c>
-      <c r="B15" t="str">
-        <v>KANIKA BISHT</v>
+      <c r="B15" t="s">
+        <v>22</v>
       </c>
       <c r="C15">
         <v>16</v>
@@ -806,25 +966,25 @@
       <c r="F15">
         <v>6</v>
       </c>
-      <c r="G15" t="str">
-        <v>ab</v>
-      </c>
-      <c r="H15" t="str">
-        <v>ab</v>
-      </c>
-      <c r="I15" t="str">
-        <v>ab</v>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
       </c>
       <c r="J15">
         <v>18</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>11</v>
       </c>
-      <c r="B16" t="str">
-        <v>KARAN</v>
+      <c r="B16" t="s">
+        <v>23</v>
       </c>
       <c r="C16">
         <v>11</v>
@@ -847,16 +1007,19 @@
       <c r="I16">
         <v>6</v>
       </c>
-      <c r="J16" t="str">
-        <v>ab</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>12</v>
       </c>
-      <c r="B17" t="str">
-        <v>NITIN BISHT</v>
+      <c r="B17" t="s">
+        <v>24</v>
       </c>
       <c r="C17">
         <v>14</v>
@@ -882,13 +1045,16 @@
       <c r="J17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="K17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>13</v>
       </c>
-      <c r="B18" t="str">
-        <v xml:space="preserve">PARTH </v>
+      <c r="B18" t="s">
+        <v>25</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -911,16 +1077,19 @@
       <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18" t="str">
-        <v>ab</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
-      <c r="B19" t="str">
-        <v>PRIYANKA</v>
+      <c r="B19" t="s">
+        <v>26</v>
       </c>
       <c r="C19">
         <v>16</v>
@@ -940,19 +1109,22 @@
       <c r="H19">
         <v>4</v>
       </c>
-      <c r="I19" t="str">
-        <v>ab</v>
+      <c r="I19" t="s">
+        <v>15</v>
       </c>
       <c r="J19">
         <v>14</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="K19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>15</v>
       </c>
-      <c r="B20" t="str">
-        <v>RAJ</v>
+      <c r="B20" t="s">
+        <v>27</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -978,13 +1150,16 @@
       <c r="J20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16</v>
       </c>
-      <c r="B21" t="str">
-        <v>RITIKA</v>
+      <c r="B21" t="s">
+        <v>28</v>
       </c>
       <c r="C21">
         <v>11</v>
@@ -995,8 +1170,8 @@
       <c r="E21">
         <v>15</v>
       </c>
-      <c r="F21" t="str">
-        <v>ab</v>
+      <c r="F21" t="s">
+        <v>15</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -1004,19 +1179,22 @@
       <c r="H21">
         <v>2</v>
       </c>
-      <c r="I21" t="str">
-        <v>ab</v>
+      <c r="I21" t="s">
+        <v>15</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="K21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>17</v>
       </c>
-      <c r="B22" t="str">
-        <v>SADHNA</v>
+      <c r="B22" t="s">
+        <v>29</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -1024,8 +1202,8 @@
       <c r="D22">
         <v>9</v>
       </c>
-      <c r="E22" t="str">
-        <v>ab</v>
+      <c r="E22" t="s">
+        <v>15</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1042,13 +1220,16 @@
       <c r="J22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="K22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>18</v>
       </c>
-      <c r="B23" t="str">
-        <v>SAKSHAM NEGI</v>
+      <c r="B23" t="s">
+        <v>30</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -1074,13 +1255,16 @@
       <c r="J23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="K23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>19</v>
       </c>
-      <c r="B24" t="str">
-        <v>SIYA SUYAL</v>
+      <c r="B24" t="s">
+        <v>31</v>
       </c>
       <c r="C24">
         <v>14</v>
@@ -1106,13 +1290,16 @@
       <c r="J24">
         <v>11</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="K24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20</v>
       </c>
-      <c r="B25" t="str">
-        <v>SPARSH BHATT</v>
+      <c r="B25" t="s">
+        <v>32</v>
       </c>
       <c r="C25">
         <v>18</v>
@@ -1126,8 +1313,8 @@
       <c r="F25">
         <v>11</v>
       </c>
-      <c r="G25" t="str">
-        <v>ab</v>
+      <c r="G25" t="s">
+        <v>15</v>
       </c>
       <c r="H25">
         <v>10</v>
@@ -1138,13 +1325,16 @@
       <c r="J25">
         <v>12</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="K25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>21</v>
       </c>
-      <c r="B26" t="str">
-        <v>TANMAY ADHIKARI</v>
+      <c r="B26" t="s">
+        <v>33</v>
       </c>
       <c r="C26">
         <v>13</v>
@@ -1170,28 +1360,31 @@
       <c r="J26">
         <v>13</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="K26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>22</v>
       </c>
-      <c r="B27" t="str">
-        <v>PALAK</v>
-      </c>
-      <c r="C27" t="str">
-        <v>ab</v>
-      </c>
-      <c r="D27" t="str">
-        <v>ab</v>
-      </c>
-      <c r="E27" t="str">
-        <v>ab</v>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
-      <c r="G27" t="str">
-        <v>ab</v>
+      <c r="G27" t="s">
+        <v>15</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1199,22 +1392,25 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" t="str">
-        <v>ab</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>23</v>
       </c>
-      <c r="B28" t="str">
-        <v xml:space="preserve">NISHANT </v>
+      <c r="B28" t="s">
+        <v>35</v>
       </c>
       <c r="C28">
         <v>13</v>
       </c>
-      <c r="D28" t="str">
-        <v>ab</v>
+      <c r="D28" t="s">
+        <v>15</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -1234,24 +1430,32 @@
       <c r="J28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="K28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>24</v>
       </c>
-      <c r="B29" t="str">
-        <v>souvik</v>
-      </c>
-      <c r="I29" t="str">
-        <v>ab</v>
-      </c>
-      <c r="J29" t="str">
-        <v>ab</v>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
+    <ignoredError sqref="A1:J2 A4:J17 A3:I3 A19:J29 A18:I18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirti\OneDrive\Desktop\mydiarykv\class test\class test 12\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9BC2C5-3026-41D0-9363-DA8430614094}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -521,24 +521,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="9" width="9.9140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -570,7 +570,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -603,7 +603,7 @@
       </c>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -632,10 +632,10 @@
         <v>20</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -666,8 +666,11 @@
       <c r="J6">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -702,7 +705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
@@ -737,7 +740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4</v>
       </c>
@@ -772,7 +775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5</v>
       </c>
@@ -807,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>6</v>
       </c>
@@ -842,7 +845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>7</v>
       </c>
@@ -877,7 +880,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>8</v>
       </c>
@@ -912,7 +915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>9</v>
       </c>
@@ -947,7 +950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10</v>
       </c>
@@ -978,8 +981,11 @@
       <c r="J15">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>11</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>12</v>
       </c>
@@ -1049,7 +1055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>13</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1119,7 +1125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1189,7 +1195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20</v>
       </c>
@@ -1329,7 +1335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1364,7 +1370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>22</v>
       </c>
@@ -1399,7 +1405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>23</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>24</v>
       </c>

--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9BC2C5-3026-41D0-9363-DA8430614094}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31F49860-9658-4F68-8F96-D71865C6419B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>31/07/2026)</t>
+  </si>
+  <si>
+    <t>CH 8</t>
+  </si>
+  <si>
+    <t>AB</t>
   </si>
 </sst>
 </file>
@@ -196,6 +202,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,6 +536,8 @@
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="9" width="9.9140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -569,6 +581,9 @@
       <c r="K3" t="s">
         <v>38</v>
       </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -601,7 +616,9 @@
       <c r="K4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1">
+        <v>46238</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
@@ -632,6 +649,9 @@
         <v>20</v>
       </c>
       <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
         <v>20</v>
       </c>
     </row>
@@ -669,6 +689,9 @@
       <c r="K6">
         <v>1</v>
       </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -704,6 +727,9 @@
       <c r="K7">
         <v>8</v>
       </c>
+      <c r="L7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -739,6 +765,9 @@
       <c r="K8">
         <v>3</v>
       </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -774,6 +803,9 @@
       <c r="K9">
         <v>8</v>
       </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -809,6 +841,9 @@
       <c r="K10">
         <v>1</v>
       </c>
+      <c r="L10">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -844,6 +879,9 @@
       <c r="K11">
         <v>18</v>
       </c>
+      <c r="L11">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -879,6 +917,9 @@
       <c r="K12">
         <v>16</v>
       </c>
+      <c r="L12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -913,6 +954,9 @@
       </c>
       <c r="K13">
         <v>4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -949,6 +993,9 @@
       <c r="K14">
         <v>6</v>
       </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -984,6 +1031,9 @@
       <c r="K15" t="s">
         <v>15</v>
       </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1019,8 +1069,11 @@
       <c r="K16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>12</v>
       </c>
@@ -1054,8 +1107,11 @@
       <c r="K17">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>13</v>
       </c>
@@ -1089,8 +1145,11 @@
       <c r="K18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1124,8 +1183,11 @@
       <c r="K19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1159,8 +1221,11 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1194,8 +1259,11 @@
       <c r="K21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1229,8 +1297,11 @@
       <c r="K22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1264,8 +1335,11 @@
       <c r="K23">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1299,8 +1373,11 @@
       <c r="K24">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20</v>
       </c>
@@ -1334,8 +1411,11 @@
       <c r="K25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1369,8 +1449,11 @@
       <c r="K26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>22</v>
       </c>
@@ -1404,8 +1487,11 @@
       <c r="K27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>23</v>
       </c>
@@ -1439,8 +1525,11 @@
       <c r="K28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>24</v>
       </c>
@@ -1455,6 +1544,9 @@
       </c>
       <c r="K29" t="s">
         <v>15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31F49860-9658-4F68-8F96-D71865C6419B}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EA3BDCF-0673-44C1-909E-1A1DAB883BE3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CT" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CT!$A$5:$F$5</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -142,13 +142,16 @@
     <t>ch7(definite Intrgral)</t>
   </si>
   <si>
-    <t>31/07/2026)</t>
-  </si>
-  <si>
     <t>CH 8</t>
   </si>
   <si>
     <t>AB</t>
+  </si>
+  <si>
+    <t>ch9</t>
+  </si>
+  <si>
+    <t>MM</t>
   </si>
 </sst>
 </file>
@@ -184,9 +187,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -202,10 +211,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,27 +535,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.9140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" customWidth="1"/>
+    <col min="12" max="13" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -575,18 +581,21 @@
       <c r="I3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="1">
@@ -613,16 +622,19 @@
       <c r="J4" s="1">
         <v>46231</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>39</v>
+      <c r="K4" s="1">
+        <v>46234</v>
       </c>
       <c r="L4" s="1">
         <v>46238</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="M4" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -654,906 +666,986 @@
       <c r="L5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="M5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I6">
+      <c r="I7">
         <v>9</v>
       </c>
-      <c r="J6">
+      <c r="J7">
         <v>7</v>
       </c>
-      <c r="K6">
+      <c r="K7">
         <v>1</v>
       </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
         <v>13</v>
       </c>
-      <c r="E7">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>6</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>13</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
       </c>
       <c r="J8">
         <v>14</v>
       </c>
       <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <v>13</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>3</v>
       </c>
-      <c r="L8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>4</v>
-      </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>15</v>
       </c>
       <c r="F9">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G9">
         <v>7</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="G10">
         <v>7</v>
       </c>
       <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="I10">
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J10">
-        <v>8</v>
-      </c>
-      <c r="K10">
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="L10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="L11">
+        <v>11</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>18</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>16</v>
       </c>
-      <c r="E11">
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <v>20</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>20</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
         <v>18</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="M12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>17</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>18</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>19</v>
       </c>
-      <c r="F12">
+      <c r="F13">
         <v>13</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>8.5</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>14</v>
       </c>
-      <c r="I12">
+      <c r="I13">
         <v>17</v>
       </c>
-      <c r="J12">
+      <c r="J13">
         <v>19</v>
       </c>
-      <c r="K12">
+      <c r="K13">
         <v>16</v>
       </c>
-      <c r="L12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13">
+      <c r="L13">
+        <v>11</v>
+      </c>
+      <c r="M13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>4</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>3</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>2</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13">
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14">
         <v>3</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>5</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>4</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="M14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>9</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="D14">
-        <v>8</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14">
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15">
         <v>5.5</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14">
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15">
         <v>2</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>13</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>14</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>6</v>
       </c>
-      <c r="L14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="L15">
+        <v>8</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>10</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>16</v>
       </c>
-      <c r="D15">
-        <v>15</v>
-      </c>
-      <c r="E15">
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
         <v>17</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <v>6</v>
       </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16">
         <v>18</v>
       </c>
-      <c r="K15" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <v>8</v>
+      </c>
+      <c r="M16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="C16">
-        <v>11</v>
-      </c>
-      <c r="D16">
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>6</v>
       </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="G16">
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17">
         <v>7</v>
       </c>
-      <c r="H16">
+      <c r="H17">
         <v>5</v>
       </c>
-      <c r="I16">
+      <c r="I17">
         <v>6</v>
       </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16">
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17">
         <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17">
-        <v>15</v>
-      </c>
-      <c r="F17">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>11</v>
-      </c>
-      <c r="H17">
-        <v>9</v>
-      </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
-      <c r="J17">
-        <v>4</v>
-      </c>
-      <c r="K17">
-        <v>12</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>9</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>12</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="C18">
-        <v>15</v>
-      </c>
-      <c r="D18">
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
         <v>19</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>19</v>
       </c>
-      <c r="F18">
+      <c r="F19">
         <v>19</v>
       </c>
-      <c r="G18">
+      <c r="G19">
         <v>5</v>
       </c>
-      <c r="H18">
+      <c r="H19">
         <v>19</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>10</v>
       </c>
-      <c r="J18">
-        <v>20</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19">
-        <v>16</v>
-      </c>
-      <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>20</v>
-      </c>
-      <c r="F19">
-        <v>16</v>
-      </c>
-      <c r="G19">
-        <v>11</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
       <c r="J19">
-        <v>14</v>
-      </c>
-      <c r="K19">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
       </c>
       <c r="L19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
+      </c>
+      <c r="F20">
+        <v>16</v>
+      </c>
+      <c r="G20">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20">
+        <v>9</v>
+      </c>
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>4</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>5</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <v>4</v>
       </c>
-      <c r="F20">
+      <c r="F21">
         <v>5</v>
       </c>
-      <c r="G20">
-        <v>8</v>
-      </c>
-      <c r="H20">
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21">
         <v>0</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>2</v>
       </c>
-      <c r="J20">
+      <c r="J21">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K21">
         <v>0</v>
       </c>
-      <c r="L20">
+      <c r="L21">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="M21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>16</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="C21">
-        <v>11</v>
-      </c>
-      <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="E21">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>8</v>
-      </c>
-      <c r="H21">
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22">
         <v>2</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21">
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22">
         <v>7</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>10</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="M22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>29</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>18</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>9</v>
       </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22">
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23">
         <v>0</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>9</v>
-      </c>
-      <c r="H22">
-        <v>4</v>
-      </c>
-      <c r="I22">
-        <v>6</v>
-      </c>
-      <c r="J22">
-        <v>4</v>
-      </c>
-      <c r="K22">
-        <v>9</v>
-      </c>
-      <c r="L22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23">
-        <v>10</v>
-      </c>
-      <c r="D23">
-        <v>8</v>
-      </c>
-      <c r="E23">
-        <v>13</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
       <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
+      <c r="L23">
         <v>7</v>
       </c>
-      <c r="J23">
+      <c r="M23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>7</v>
+      </c>
+      <c r="J24">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>6</v>
       </c>
-      <c r="L23">
+      <c r="L24">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="M24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>31</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>14</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>16</v>
       </c>
-      <c r="E24">
-        <v>15</v>
-      </c>
-      <c r="F24">
+      <c r="E25">
+        <v>15</v>
+      </c>
+      <c r="F25">
         <v>16</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>17</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>3</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>16</v>
       </c>
-      <c r="J24">
-        <v>11</v>
-      </c>
-      <c r="K24">
-        <v>11</v>
-      </c>
-      <c r="L24">
+      <c r="J25">
+        <v>11</v>
+      </c>
+      <c r="K25">
+        <v>11</v>
+      </c>
+      <c r="L25">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="M25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
         <v>32</v>
       </c>
-      <c r="C25">
+      <c r="C26">
         <v>18</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>18</v>
       </c>
-      <c r="E25">
-        <v>20</v>
-      </c>
-      <c r="F25">
-        <v>11</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25">
+      <c r="E26">
+        <v>20</v>
+      </c>
+      <c r="F26">
+        <v>11</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26">
         <v>10</v>
       </c>
-      <c r="I25">
-        <v>15</v>
-      </c>
-      <c r="J25">
+      <c r="I26">
+        <v>15</v>
+      </c>
+      <c r="J26">
         <v>12</v>
       </c>
-      <c r="K25">
+      <c r="K26">
         <v>5</v>
       </c>
-      <c r="L25">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="L26">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>21</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>13</v>
       </c>
-      <c r="D26">
-        <v>11</v>
-      </c>
-      <c r="E26">
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="E27">
         <v>17</v>
       </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="G26">
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
         <v>12</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>9</v>
       </c>
-      <c r="I26">
+      <c r="I27">
         <v>12</v>
       </c>
-      <c r="J26">
+      <c r="J27">
         <v>13</v>
       </c>
-      <c r="K26">
+      <c r="K27">
         <v>4</v>
       </c>
-      <c r="L26">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="L27">
+        <v>8</v>
+      </c>
+      <c r="M27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27">
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28">
         <v>3</v>
       </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27">
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="I28">
         <v>0</v>
       </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>23</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>35</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>13</v>
       </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28">
-        <v>15</v>
-      </c>
-      <c r="F28">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>11</v>
-      </c>
-      <c r="H28">
-        <v>8</v>
-      </c>
-      <c r="I28">
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>11</v>
+      </c>
+      <c r="H29">
+        <v>8</v>
+      </c>
+      <c r="I29">
         <v>9</v>
       </c>
-      <c r="J28">
+      <c r="J29">
         <v>6</v>
       </c>
-      <c r="K28">
+      <c r="K29">
         <v>2</v>
       </c>
-      <c r="L28">
+      <c r="L29">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="M29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>24</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>36</v>
       </c>
-      <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>41</v>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J2 A4:J17 A3:I3 A19:J29 A18:I18" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J2 A7:J18 A3:I3 A20:J30 A19:I19 C4:J4 A5 C5:J5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EA3BDCF-0673-44C1-909E-1A1DAB883BE3}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527A3EA3-0EC5-45F6-8988-AD7E91B999DA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,6 +211,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1553,7 +1557,7 @@
         <v>15</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1645,7 +1649,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J2 A7:J18 A3:I3 A20:J30 A19:I19 C4:J4 A5 C5:J5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J2 A7:J18 A3:I3 A20:J27 A19:I19 C4:J4 A5 C5:J5 A29:J30 A28:E28 G28:J28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527A3EA3-0EC5-45F6-8988-AD7E91B999DA}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A58C513-568C-4BAD-98EE-9E5E57F9BA15}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>MM</t>
+  </si>
+  <si>
+    <t>MT-4</t>
   </si>
 </sst>
 </file>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
@@ -550,17 +553,17 @@
     <col min="12" max="13" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -597,8 +600,11 @@
       <c r="M3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -635,8 +641,11 @@
       <c r="M4" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4" s="1">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
@@ -673,13 +682,16 @@
       <c r="M5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -719,8 +731,11 @@
       <c r="M7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -760,8 +775,11 @@
       <c r="M8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -801,8 +819,11 @@
       <c r="M9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
@@ -842,8 +863,11 @@
       <c r="M10">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5</v>
       </c>
@@ -883,8 +907,11 @@
       <c r="M11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
@@ -924,8 +951,11 @@
       <c r="M12">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>7</v>
       </c>
@@ -965,8 +995,11 @@
       <c r="M13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>8</v>
       </c>
@@ -1006,8 +1039,11 @@
       <c r="M14">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>9</v>
       </c>
@@ -1047,8 +1083,11 @@
       <c r="M15">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="M16">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>11</v>
       </c>
@@ -1129,8 +1171,11 @@
       <c r="M17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>12</v>
       </c>
@@ -1170,8 +1215,11 @@
       <c r="M18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>13</v>
       </c>
@@ -1211,8 +1259,11 @@
       <c r="M19">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
@@ -1252,8 +1303,11 @@
       <c r="M20">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>15</v>
       </c>
@@ -1293,8 +1347,11 @@
       <c r="M21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1334,8 +1391,11 @@
       <c r="M22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>17</v>
       </c>
@@ -1375,8 +1435,11 @@
       <c r="M23">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>18</v>
       </c>
@@ -1416,8 +1479,11 @@
       <c r="M24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1457,8 +1523,11 @@
       <c r="M25">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20</v>
       </c>
@@ -1498,8 +1567,11 @@
       <c r="M26">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>21</v>
       </c>
@@ -1539,8 +1611,11 @@
       <c r="M27">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>22</v>
       </c>
@@ -1580,8 +1655,11 @@
       <c r="M28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>23</v>
       </c>
@@ -1621,8 +1699,11 @@
       <c r="M29">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>24</v>
       </c>
@@ -1643,6 +1724,9 @@
       </c>
       <c r="M30">
         <v>13</v>
+      </c>
+      <c r="N30">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
